--- a/research/traditional_assets/database/data/lithuania/lithuania_apparel.xlsx
+++ b/research/traditional_assets/database/data/lithuania/lithuania_apparel.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0757</v>
+        <v>-0.0394</v>
       </c>
       <c r="G2">
-        <v>-0.0685878962536023</v>
+        <v>-0.02962825278810409</v>
       </c>
       <c r="H2">
-        <v>-0.0685878962536023</v>
+        <v>-0.02962825278810409</v>
       </c>
       <c r="I2">
-        <v>-0.06080691642651296</v>
+        <v>-0.05055762081784387</v>
       </c>
       <c r="J2">
-        <v>-0.06080691642651296</v>
+        <v>-0.05055762081784387</v>
       </c>
       <c r="K2">
-        <v>-2.84</v>
+        <v>-1.69</v>
       </c>
       <c r="L2">
-        <v>-0.08184438040345821</v>
+        <v>-0.06282527881040892</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +630,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.472</v>
+        <v>0.552</v>
       </c>
       <c r="V2">
-        <v>0.07375</v>
+        <v>0.1095238095238095</v>
       </c>
       <c r="W2">
-        <v>-0.2857142857142857</v>
+        <v>-0.3152985074626866</v>
       </c>
       <c r="X2">
-        <v>0.1606206765205524</v>
+        <v>0.1401793435510312</v>
       </c>
       <c r="Y2">
-        <v>-0.446334962234838</v>
+        <v>-0.4554778510137177</v>
       </c>
       <c r="Z2">
-        <v>2.289673375123721</v>
+        <v>2.22350801785419</v>
       </c>
       <c r="AA2">
-        <v>-0.13922797756516</v>
+        <v>-0.1124152752521078</v>
       </c>
       <c r="AB2">
-        <v>0.1049592289403618</v>
+        <v>0.08722620381456839</v>
       </c>
       <c r="AC2">
-        <v>-0.2441872065055218</v>
+        <v>-0.1996414790666762</v>
       </c>
       <c r="AD2">
-        <v>7.21</v>
+        <v>7.38</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>7.21</v>
+        <v>7.38</v>
       </c>
       <c r="AG2">
-        <v>6.738</v>
+        <v>6.827999999999999</v>
       </c>
       <c r="AH2">
-        <v>0.5297575312270389</v>
+        <v>0.5942028985507246</v>
       </c>
       <c r="AI2">
-        <v>0.5650470219435737</v>
+        <v>0.7158098933074685</v>
       </c>
       <c r="AJ2">
-        <v>0.512863449535698</v>
+        <v>0.5753286147623863</v>
       </c>
       <c r="AK2">
-        <v>0.54833984375</v>
+        <v>0.6997335519573683</v>
       </c>
       <c r="AL2">
-        <v>0.25</v>
+        <v>0.427</v>
       </c>
       <c r="AM2">
-        <v>0.179</v>
+        <v>0.427</v>
       </c>
       <c r="AN2">
-        <v>-5.421052631578947</v>
+        <v>-7.826086956521739</v>
       </c>
       <c r="AO2">
-        <v>-8.44</v>
+        <v>-3.185011709601874</v>
       </c>
       <c r="AP2">
-        <v>-5.066165413533834</v>
+        <v>-7.240721102863202</v>
       </c>
       <c r="AQ2">
-        <v>-11.7877094972067</v>
+        <v>-3.185011709601874</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +716,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0757</v>
+        <v>-0.0394</v>
       </c>
       <c r="G3">
-        <v>-0.0685878962536023</v>
+        <v>-0.02962825278810409</v>
       </c>
       <c r="H3">
-        <v>-0.0685878962536023</v>
+        <v>-0.02962825278810409</v>
       </c>
       <c r="I3">
-        <v>-0.06080691642651296</v>
+        <v>-0.05055762081784387</v>
       </c>
       <c r="J3">
-        <v>-0.06080691642651296</v>
+        <v>-0.05055762081784387</v>
       </c>
       <c r="K3">
-        <v>-2.84</v>
+        <v>-1.69</v>
       </c>
       <c r="L3">
-        <v>-0.08184438040345821</v>
+        <v>-0.06282527881040892</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,73 +758,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.472</v>
+        <v>0.552</v>
       </c>
       <c r="V3">
-        <v>0.07375</v>
+        <v>0.1095238095238095</v>
       </c>
       <c r="W3">
-        <v>-0.2857142857142857</v>
+        <v>-0.3152985074626866</v>
       </c>
       <c r="X3">
-        <v>0.1606206765205524</v>
+        <v>0.1401793435510312</v>
       </c>
       <c r="Y3">
-        <v>-0.446334962234838</v>
+        <v>-0.4554778510137177</v>
       </c>
       <c r="Z3">
-        <v>2.289673375123721</v>
+        <v>2.22350801785419</v>
       </c>
       <c r="AA3">
-        <v>-0.13922797756516</v>
+        <v>-0.1124152752521078</v>
       </c>
       <c r="AB3">
-        <v>0.1049592289403618</v>
+        <v>0.08722620381456839</v>
       </c>
       <c r="AC3">
-        <v>-0.2441872065055218</v>
+        <v>-0.1996414790666762</v>
       </c>
       <c r="AD3">
-        <v>7.21</v>
+        <v>7.38</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>7.21</v>
+        <v>7.38</v>
       </c>
       <c r="AG3">
-        <v>6.738</v>
+        <v>6.827999999999999</v>
       </c>
       <c r="AH3">
-        <v>0.5297575312270389</v>
+        <v>0.5942028985507246</v>
       </c>
       <c r="AI3">
-        <v>0.5650470219435737</v>
+        <v>0.7158098933074685</v>
       </c>
       <c r="AJ3">
-        <v>0.512863449535698</v>
+        <v>0.5753286147623863</v>
       </c>
       <c r="AK3">
-        <v>0.54833984375</v>
+        <v>0.6997335519573683</v>
       </c>
       <c r="AL3">
-        <v>0.25</v>
+        <v>0.427</v>
       </c>
       <c r="AM3">
-        <v>0.179</v>
+        <v>0.427</v>
       </c>
       <c r="AN3">
-        <v>-5.421052631578947</v>
+        <v>-7.826086956521739</v>
       </c>
       <c r="AO3">
-        <v>-8.44</v>
+        <v>-3.185011709601874</v>
       </c>
       <c r="AP3">
-        <v>-5.066165413533834</v>
+        <v>-7.240721102863202</v>
       </c>
       <c r="AQ3">
-        <v>-11.7877094972067</v>
+        <v>-3.185011709601874</v>
       </c>
     </row>
   </sheetData>
